--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92874</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B2" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R2" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R3" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373390</v>
       </c>
       <c r="B4" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373457</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129373390</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373457</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R2" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R3" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R2" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R3" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R2" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R3" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129373390</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79102</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373457</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79070</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129373390</v>
       </c>
       <c r="B4" t="n">
-        <v>79102</v>
+        <v>79107</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373457</v>
       </c>
       <c r="B6" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R2" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R3" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129373390</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373457</v>
       </c>
       <c r="B6" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79076</v>
+        <v>79113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79108</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>129373390</v>
       </c>
       <c r="B4" t="n">
-        <v>79108</v>
+        <v>79113</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>129373435</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>92913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>129373457</v>
       </c>
       <c r="B6" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B2" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R2" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R3" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 45607-2025 artfynd.xlsx
+++ b/artfynd/A 45607-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129373447</v>
+        <v>129373388</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>663460</v>
+        <v>663511</v>
       </c>
       <c r="R2" t="n">
-        <v>6987790</v>
+        <v>6987755</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129373388</v>
+        <v>129373447</v>
       </c>
       <c r="B3" t="n">
-        <v>79113</v>
+        <v>79081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>663511</v>
+        <v>663460</v>
       </c>
       <c r="R3" t="n">
-        <v>6987755</v>
+        <v>6987790</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
